--- a/Datos limpios/Pricing diario/2025/Maiz.xlsx
+++ b/Datos limpios/Pricing diario/2025/Maiz.xlsx
@@ -10596,298 +10596,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100D6CA5EAACE9DA04D9E421A617A76D009" ma:contentTypeVersion="19" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="854b0670eee28d8fa271d4f22cb9c97d">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="77131357-5c03-45fa-a80b-b9111bb46cb1" xmlns:ns3="d3f11db4-a96c-41b4-b8ec-902c72f52048" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b486ba09ce8a2fb19cc660d7edf32df4" ns2:_="" ns3:_="">
-    <xsd:import namespace="77131357-5c03-45fa-a80b-b9111bb46cb1"/>
-    <xsd:import namespace="d3f11db4-a96c-41b4-b8ec-902c72f52048"/>
-    <xsd:element name="properties">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element name="documentManagement">
-            <xsd:complexType>
-              <xsd:all>
-                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns2:_Flow_SignoffStatus" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
-              </xsd:all>
-            </xsd:complexType>
-          </xsd:element>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="77131357-5c03-45fa-a80b-b9111bb46cb1" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="10" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="11" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="12" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="13" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="14" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="15" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="16" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="17" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="_Flow_SignoffStatus" ma:index="20" nillable="true" ma:displayName="Estado de aprobación" ma:internalName="Estado_x0020_de_x0020_aprobaci_x00f3_n">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="21" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="23" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="6ab20cb4-9c0f-41d2-89f3-02c382a657d6" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="25" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:description="" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="26" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="d3f11db4-a96c-41b4-b8ec-902c72f52048" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="18" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
-            <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="19" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="TaxCatchAll" ma:index="24" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{ac6aff7b-77d9-4645-af3f-7b0008d975fa}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="d3f11db4-a96c-41b4-b8ec-902c72f52048">
-      <xsd:complexType>
-        <xsd:complexContent>
-          <xsd:extension base="dms:MultiChoiceLookup">
-            <xsd:sequence>
-              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
-            </xsd:sequence>
-          </xsd:extension>
-        </xsd:complexContent>
-      </xsd:complexType>
-    </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
-    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
-    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
-    <xsd:element name="coreProperties" type="CT_coreProperties"/>
-    <xsd:complexType name="CT_coreProperties">
-      <xsd:all>
-        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
-        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
-        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
-          <xsd:annotation>
-            <xsd:documentation>
-                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
-                    </xsd:documentation>
-          </xsd:annotation>
-        </xsd:element>
-        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
-      </xsd:all>
-    </xsd:complexType>
-  </xsd:schema>
-  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
-    <xs:element name="Person">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:DisplayName" minOccurs="0"/>
-          <xs:element ref="pc:AccountId" minOccurs="0"/>
-          <xs:element ref="pc:AccountType" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="DisplayName" type="xs:string"/>
-    <xs:element name="AccountId" type="xs:string"/>
-    <xs:element name="AccountType" type="xs:string"/>
-    <xs:element name="BDCAssociatedEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-        <xs:attribute ref="pc:EntityNamespace"/>
-        <xs:attribute ref="pc:EntityName"/>
-        <xs:attribute ref="pc:SystemInstanceName"/>
-        <xs:attribute ref="pc:AssociationName"/>
-      </xs:complexType>
-    </xs:element>
-    <xs:attribute name="EntityNamespace" type="xs:string"/>
-    <xs:attribute name="EntityName" type="xs:string"/>
-    <xs:attribute name="SystemInstanceName" type="xs:string"/>
-    <xs:attribute name="AssociationName" type="xs:string"/>
-    <xs:element name="BDCEntity">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
-          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
-          <xs:element ref="pc:EntityId1" minOccurs="0"/>
-          <xs:element ref="pc:EntityId2" minOccurs="0"/>
-          <xs:element ref="pc:EntityId3" minOccurs="0"/>
-          <xs:element ref="pc:EntityId4" minOccurs="0"/>
-          <xs:element ref="pc:EntityId5" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="EntityDisplayName" type="xs:string"/>
-    <xs:element name="EntityInstanceReference" type="xs:string"/>
-    <xs:element name="EntityId1" type="xs:string"/>
-    <xs:element name="EntityId2" type="xs:string"/>
-    <xs:element name="EntityId3" type="xs:string"/>
-    <xs:element name="EntityId4" type="xs:string"/>
-    <xs:element name="EntityId5" type="xs:string"/>
-    <xs:element name="Terms">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermInfo">
-      <xs:complexType>
-        <xs:sequence>
-          <xs:element ref="pc:TermName" minOccurs="0"/>
-          <xs:element ref="pc:TermId" minOccurs="0"/>
-        </xs:sequence>
-      </xs:complexType>
-    </xs:element>
-    <xs:element name="TermName" type="xs:string"/>
-    <xs:element name="TermId" type="xs:string"/>
-  </xs:schema>
-</ct:contentTypeSchema>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_Flow_SignoffStatus xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1" xsi:nil="true"/>
-    <TaxCatchAll xmlns="d3f11db4-a96c-41b4-b8ec-902c72f52048" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="77131357-5c03-45fa-a80b-b9111bb46cb1">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{3162F895-9E74-4B53-8B1C-2A6E9AFE2241}"/>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2EB43969-4071-4241-B8DC-6DE6F33F6E84}"/>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9374F3E2-D6E6-4974-B971-C4449BC72689}"/>
 </file>
--- a/Datos limpios/Pricing diario/2025/Maiz.xlsx
+++ b/Datos limpios/Pricing diario/2025/Maiz.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K276"/>
+  <dimension ref="A1:K300"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="20.7109375" style="2" customWidth="1"/>
@@ -10561,19 +10561,19 @@
         <v>45957</v>
       </c>
       <c r="B276">
-        <v>1510</v>
+        <v>53856.24</v>
       </c>
       <c r="C276">
-        <v>0</v>
+        <v>658.8200000000001</v>
       </c>
       <c r="D276">
-        <v>0</v>
+        <v>862.59</v>
       </c>
       <c r="E276">
-        <v>1510</v>
+        <v>53652.47</v>
       </c>
       <c r="F276">
-        <v>0</v>
+        <v>10947.52</v>
       </c>
       <c r="G276">
         <v>0</v>
@@ -10582,12 +10582,900 @@
         <v>0</v>
       </c>
       <c r="I276">
-        <v>0</v>
+        <v>10947.52</v>
       </c>
       <c r="J276">
-        <v>1510</v>
+        <v>64599.99000000001</v>
       </c>
       <c r="K276" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="277">
+      <c r="A277" s="2">
+        <v>45958</v>
+      </c>
+      <c r="B277">
+        <v>100329.19</v>
+      </c>
+      <c r="C277">
+        <v>2478.38</v>
+      </c>
+      <c r="D277">
+        <v>0</v>
+      </c>
+      <c r="E277">
+        <v>102807.57</v>
+      </c>
+      <c r="F277">
+        <v>14310.69</v>
+      </c>
+      <c r="G277">
+        <v>0</v>
+      </c>
+      <c r="H277">
+        <v>0</v>
+      </c>
+      <c r="I277">
+        <v>14310.69</v>
+      </c>
+      <c r="J277">
+        <v>117118.26</v>
+      </c>
+      <c r="K277" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="278">
+      <c r="A278" s="2">
+        <v>45959</v>
+      </c>
+      <c r="B278">
+        <v>55249.1</v>
+      </c>
+      <c r="C278">
+        <v>270.16</v>
+      </c>
+      <c r="D278">
+        <v>210.16</v>
+      </c>
+      <c r="E278">
+        <v>55309.1</v>
+      </c>
+      <c r="F278">
+        <v>40061.28</v>
+      </c>
+      <c r="G278">
+        <v>100</v>
+      </c>
+      <c r="H278">
+        <v>0</v>
+      </c>
+      <c r="I278">
+        <v>40161.28</v>
+      </c>
+      <c r="J278">
+        <v>95470.38</v>
+      </c>
+      <c r="K278" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="279">
+      <c r="A279" s="2">
+        <v>45960</v>
+      </c>
+      <c r="B279">
+        <v>74464.46000000001</v>
+      </c>
+      <c r="C279">
+        <v>161.33</v>
+      </c>
+      <c r="D279">
+        <v>1100</v>
+      </c>
+      <c r="E279">
+        <v>73525.79000000001</v>
+      </c>
+      <c r="F279">
+        <v>56677.22</v>
+      </c>
+      <c r="G279">
+        <v>0</v>
+      </c>
+      <c r="H279">
+        <v>0</v>
+      </c>
+      <c r="I279">
+        <v>56677.22</v>
+      </c>
+      <c r="J279">
+        <v>130203.01</v>
+      </c>
+      <c r="K279" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="280">
+      <c r="A280" s="2">
+        <v>45961</v>
+      </c>
+      <c r="B280">
+        <v>89175.99000000001</v>
+      </c>
+      <c r="C280">
+        <v>1590</v>
+      </c>
+      <c r="D280">
+        <v>34.51</v>
+      </c>
+      <c r="E280">
+        <v>90731.48000000001</v>
+      </c>
+      <c r="F280">
+        <v>58011.74</v>
+      </c>
+      <c r="G280">
+        <v>2000</v>
+      </c>
+      <c r="H280">
+        <v>4000</v>
+      </c>
+      <c r="I280">
+        <v>56011.74</v>
+      </c>
+      <c r="J280">
+        <v>146743.22</v>
+      </c>
+      <c r="K280" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="281">
+      <c r="A281" s="2">
+        <v>45962</v>
+      </c>
+      <c r="B281">
+        <v>159.87</v>
+      </c>
+      <c r="C281">
+        <v>0</v>
+      </c>
+      <c r="D281">
+        <v>0</v>
+      </c>
+      <c r="E281">
+        <v>159.87</v>
+      </c>
+      <c r="F281">
+        <v>0</v>
+      </c>
+      <c r="G281">
+        <v>0</v>
+      </c>
+      <c r="H281">
+        <v>0</v>
+      </c>
+      <c r="I281">
+        <v>0</v>
+      </c>
+      <c r="J281">
+        <v>159.87</v>
+      </c>
+      <c r="K281" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="282">
+      <c r="A282" s="2">
+        <v>45963</v>
+      </c>
+      <c r="B282">
+        <v>0</v>
+      </c>
+      <c r="C282">
+        <v>0</v>
+      </c>
+      <c r="D282">
+        <v>0</v>
+      </c>
+      <c r="E282">
+        <v>0</v>
+      </c>
+      <c r="F282">
+        <v>0</v>
+      </c>
+      <c r="G282">
+        <v>0</v>
+      </c>
+      <c r="H282">
+        <v>0</v>
+      </c>
+      <c r="I282">
+        <v>0</v>
+      </c>
+      <c r="J282">
+        <v>0</v>
+      </c>
+      <c r="K282" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" s="2">
+        <v>45964</v>
+      </c>
+      <c r="B283">
+        <v>84486.81</v>
+      </c>
+      <c r="C283">
+        <v>2034.51</v>
+      </c>
+      <c r="D283">
+        <v>700</v>
+      </c>
+      <c r="E283">
+        <v>85821.31999999999</v>
+      </c>
+      <c r="F283">
+        <v>51734.77</v>
+      </c>
+      <c r="G283">
+        <v>0</v>
+      </c>
+      <c r="H283">
+        <v>300</v>
+      </c>
+      <c r="I283">
+        <v>51434.77</v>
+      </c>
+      <c r="J283">
+        <v>137256.09</v>
+      </c>
+      <c r="K283" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" s="2">
+        <v>45965</v>
+      </c>
+      <c r="B284">
+        <v>75165.13</v>
+      </c>
+      <c r="C284">
+        <v>1477.26</v>
+      </c>
+      <c r="D284">
+        <v>237.69</v>
+      </c>
+      <c r="E284">
+        <v>76404.7</v>
+      </c>
+      <c r="F284">
+        <v>24350.74</v>
+      </c>
+      <c r="G284">
+        <v>0</v>
+      </c>
+      <c r="H284">
+        <v>0</v>
+      </c>
+      <c r="I284">
+        <v>24350.74</v>
+      </c>
+      <c r="J284">
+        <v>100755.44</v>
+      </c>
+      <c r="K284" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" s="2">
+        <v>45966</v>
+      </c>
+      <c r="B285">
+        <v>246117.89</v>
+      </c>
+      <c r="C285">
+        <v>4304</v>
+      </c>
+      <c r="D285">
+        <v>2995.04</v>
+      </c>
+      <c r="E285">
+        <v>247426.85</v>
+      </c>
+      <c r="F285">
+        <v>48673.81</v>
+      </c>
+      <c r="G285">
+        <v>65</v>
+      </c>
+      <c r="H285">
+        <v>410</v>
+      </c>
+      <c r="I285">
+        <v>48328.81</v>
+      </c>
+      <c r="J285">
+        <v>295755.66</v>
+      </c>
+      <c r="K285" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" s="2">
+        <v>45967</v>
+      </c>
+      <c r="B286">
+        <v>180382.21</v>
+      </c>
+      <c r="C286">
+        <v>5297.9</v>
+      </c>
+      <c r="D286">
+        <v>1240</v>
+      </c>
+      <c r="E286">
+        <v>184440.11</v>
+      </c>
+      <c r="F286">
+        <v>22386.36</v>
+      </c>
+      <c r="G286">
+        <v>6000</v>
+      </c>
+      <c r="H286">
+        <v>0</v>
+      </c>
+      <c r="I286">
+        <v>28386.36</v>
+      </c>
+      <c r="J286">
+        <v>212826.47</v>
+      </c>
+      <c r="K286" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" s="2">
+        <v>45968</v>
+      </c>
+      <c r="B287">
+        <v>107125.03</v>
+      </c>
+      <c r="C287">
+        <v>1639.84</v>
+      </c>
+      <c r="D287">
+        <v>6240</v>
+      </c>
+      <c r="E287">
+        <v>102524.87</v>
+      </c>
+      <c r="F287">
+        <v>24535.71</v>
+      </c>
+      <c r="G287">
+        <v>0</v>
+      </c>
+      <c r="H287">
+        <v>0</v>
+      </c>
+      <c r="I287">
+        <v>24535.71</v>
+      </c>
+      <c r="J287">
+        <v>127060.58</v>
+      </c>
+      <c r="K287" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" s="2">
+        <v>45969</v>
+      </c>
+      <c r="B288">
+        <v>516.72</v>
+      </c>
+      <c r="C288">
+        <v>0</v>
+      </c>
+      <c r="D288">
+        <v>0</v>
+      </c>
+      <c r="E288">
+        <v>516.72</v>
+      </c>
+      <c r="F288">
+        <v>0</v>
+      </c>
+      <c r="G288">
+        <v>0</v>
+      </c>
+      <c r="H288">
+        <v>0</v>
+      </c>
+      <c r="I288">
+        <v>0</v>
+      </c>
+      <c r="J288">
+        <v>516.72</v>
+      </c>
+      <c r="K288" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" s="2">
+        <v>45970</v>
+      </c>
+      <c r="B289">
+        <v>35</v>
+      </c>
+      <c r="C289">
+        <v>0</v>
+      </c>
+      <c r="D289">
+        <v>0</v>
+      </c>
+      <c r="E289">
+        <v>35</v>
+      </c>
+      <c r="F289">
+        <v>0</v>
+      </c>
+      <c r="G289">
+        <v>0</v>
+      </c>
+      <c r="H289">
+        <v>0</v>
+      </c>
+      <c r="I289">
+        <v>0</v>
+      </c>
+      <c r="J289">
+        <v>35</v>
+      </c>
+      <c r="K289" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" s="2">
+        <v>45971</v>
+      </c>
+      <c r="B290">
+        <v>141574.79</v>
+      </c>
+      <c r="C290">
+        <v>517.5700000000001</v>
+      </c>
+      <c r="D290">
+        <v>17620</v>
+      </c>
+      <c r="E290">
+        <v>124472.36</v>
+      </c>
+      <c r="F290">
+        <v>23024.65</v>
+      </c>
+      <c r="G290">
+        <v>0</v>
+      </c>
+      <c r="H290">
+        <v>150</v>
+      </c>
+      <c r="I290">
+        <v>22874.65</v>
+      </c>
+      <c r="J290">
+        <v>147347.01</v>
+      </c>
+      <c r="K290" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" s="2">
+        <v>45972</v>
+      </c>
+      <c r="B291">
+        <v>156223.2</v>
+      </c>
+      <c r="C291">
+        <v>846.9399999999999</v>
+      </c>
+      <c r="D291">
+        <v>2150</v>
+      </c>
+      <c r="E291">
+        <v>154920.14</v>
+      </c>
+      <c r="F291">
+        <v>32333.31</v>
+      </c>
+      <c r="G291">
+        <v>0</v>
+      </c>
+      <c r="H291">
+        <v>30</v>
+      </c>
+      <c r="I291">
+        <v>32303.31</v>
+      </c>
+      <c r="J291">
+        <v>187223.45</v>
+      </c>
+      <c r="K291" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" s="2">
+        <v>45973</v>
+      </c>
+      <c r="B292">
+        <v>107741.54</v>
+      </c>
+      <c r="C292">
+        <v>857</v>
+      </c>
+      <c r="D292">
+        <v>2700</v>
+      </c>
+      <c r="E292">
+        <v>105898.54</v>
+      </c>
+      <c r="F292">
+        <v>17084.26</v>
+      </c>
+      <c r="G292">
+        <v>0</v>
+      </c>
+      <c r="H292">
+        <v>0</v>
+      </c>
+      <c r="I292">
+        <v>17084.26</v>
+      </c>
+      <c r="J292">
+        <v>122982.8</v>
+      </c>
+      <c r="K292" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" s="2">
+        <v>45974</v>
+      </c>
+      <c r="B293">
+        <v>165783.29</v>
+      </c>
+      <c r="C293">
+        <v>668.0700000000001</v>
+      </c>
+      <c r="D293">
+        <v>1230</v>
+      </c>
+      <c r="E293">
+        <v>165221.36</v>
+      </c>
+      <c r="F293">
+        <v>30279.37</v>
+      </c>
+      <c r="G293">
+        <v>204.23</v>
+      </c>
+      <c r="H293">
+        <v>480</v>
+      </c>
+      <c r="I293">
+        <v>30003.6</v>
+      </c>
+      <c r="J293">
+        <v>195224.96</v>
+      </c>
+      <c r="K293" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" s="2">
+        <v>45975</v>
+      </c>
+      <c r="B294">
+        <v>321355.95</v>
+      </c>
+      <c r="C294">
+        <v>2018.02</v>
+      </c>
+      <c r="D294">
+        <v>4047.65</v>
+      </c>
+      <c r="E294">
+        <v>319326.32</v>
+      </c>
+      <c r="F294">
+        <v>40314.05</v>
+      </c>
+      <c r="G294">
+        <v>0</v>
+      </c>
+      <c r="H294">
+        <v>0</v>
+      </c>
+      <c r="I294">
+        <v>40314.05</v>
+      </c>
+      <c r="J294">
+        <v>359640.37</v>
+      </c>
+      <c r="K294" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" s="2">
+        <v>45976</v>
+      </c>
+      <c r="B295">
+        <v>1709.34</v>
+      </c>
+      <c r="C295">
+        <v>0</v>
+      </c>
+      <c r="D295">
+        <v>0</v>
+      </c>
+      <c r="E295">
+        <v>1709.34</v>
+      </c>
+      <c r="F295">
+        <v>67.13</v>
+      </c>
+      <c r="G295">
+        <v>0</v>
+      </c>
+      <c r="H295">
+        <v>0</v>
+      </c>
+      <c r="I295">
+        <v>67.13</v>
+      </c>
+      <c r="J295">
+        <v>1776.47</v>
+      </c>
+      <c r="K295" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" s="2">
+        <v>45978</v>
+      </c>
+      <c r="B296">
+        <v>85659.13</v>
+      </c>
+      <c r="C296">
+        <v>781.28</v>
+      </c>
+      <c r="D296">
+        <v>2330</v>
+      </c>
+      <c r="E296">
+        <v>84110.41</v>
+      </c>
+      <c r="F296">
+        <v>30464.67</v>
+      </c>
+      <c r="G296">
+        <v>0</v>
+      </c>
+      <c r="H296">
+        <v>630</v>
+      </c>
+      <c r="I296">
+        <v>29834.67</v>
+      </c>
+      <c r="J296">
+        <v>113945.08</v>
+      </c>
+      <c r="K296" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" s="2">
+        <v>45979</v>
+      </c>
+      <c r="B297">
+        <v>59922.54</v>
+      </c>
+      <c r="C297">
+        <v>3606.12</v>
+      </c>
+      <c r="D297">
+        <v>446.2</v>
+      </c>
+      <c r="E297">
+        <v>63082.46000000001</v>
+      </c>
+      <c r="F297">
+        <v>17647.37</v>
+      </c>
+      <c r="G297">
+        <v>150</v>
+      </c>
+      <c r="H297">
+        <v>0</v>
+      </c>
+      <c r="I297">
+        <v>17797.37</v>
+      </c>
+      <c r="J297">
+        <v>80879.83</v>
+      </c>
+      <c r="K297" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" s="2">
+        <v>45980</v>
+      </c>
+      <c r="B298">
+        <v>85408.49000000001</v>
+      </c>
+      <c r="C298">
+        <v>3900.48</v>
+      </c>
+      <c r="D298">
+        <v>1029.23</v>
+      </c>
+      <c r="E298">
+        <v>88279.74000000001</v>
+      </c>
+      <c r="F298">
+        <v>25535.4</v>
+      </c>
+      <c r="G298">
+        <v>3.25</v>
+      </c>
+      <c r="H298">
+        <v>0</v>
+      </c>
+      <c r="I298">
+        <v>25538.65</v>
+      </c>
+      <c r="J298">
+        <v>113818.39</v>
+      </c>
+      <c r="K298" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" s="2">
+        <v>45981</v>
+      </c>
+      <c r="B299">
+        <v>40224.85</v>
+      </c>
+      <c r="C299">
+        <v>170.34</v>
+      </c>
+      <c r="D299">
+        <v>0</v>
+      </c>
+      <c r="E299">
+        <v>40395.19</v>
+      </c>
+      <c r="F299">
+        <v>28373.17</v>
+      </c>
+      <c r="G299">
+        <v>0</v>
+      </c>
+      <c r="H299">
+        <v>0</v>
+      </c>
+      <c r="I299">
+        <v>28373.17</v>
+      </c>
+      <c r="J299">
+        <v>68768.36</v>
+      </c>
+      <c r="K299" t="inlineStr">
+        <is>
+          <t>MAIZ</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" s="2">
+        <v>45982</v>
+      </c>
+      <c r="B300">
+        <v>5254.32</v>
+      </c>
+      <c r="C300">
+        <v>120</v>
+      </c>
+      <c r="D300">
+        <v>0</v>
+      </c>
+      <c r="E300">
+        <v>5374.32</v>
+      </c>
+      <c r="F300">
+        <v>1674.99</v>
+      </c>
+      <c r="G300">
+        <v>0</v>
+      </c>
+      <c r="H300">
+        <v>0</v>
+      </c>
+      <c r="I300">
+        <v>1674.99</v>
+      </c>
+      <c r="J300">
+        <v>7049.309999999999</v>
+      </c>
+      <c r="K300" t="inlineStr">
         <is>
           <t>MAIZ</t>
         </is>
